--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-PAR-Close-Operation-Output.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-PAR-Close-Operation-Output.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="223">
   <si>
     <t>Property</t>
   </si>
@@ -486,6 +486,16 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Parameters.meta.tag</t>
   </si>
   <si>
@@ -612,6 +622,9 @@
     <t>The name of the parameter (reference to the operation definition).</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Parameters.parameter.value[x]</t>
   </si>
   <si>
@@ -625,24 +638,31 @@
     <t>If the parameter is a data type.</t>
   </si>
   <si>
+    <t>ele-1
+inv-1</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>If parameter is a whole resource</t>
+  </si>
+  <si>
+    <t>If the parameter is a whole resource.</t>
+  </si>
+  <si>
+    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+  </si>
+  <si>
     <t xml:space="preserve">inv-1
 </t>
   </si>
   <si>
-    <t>Parameters.parameter.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>If parameter is a whole resource</t>
-  </si>
-  <si>
-    <t>If the parameter is a whole resource.</t>
-  </si>
-  <si>
-    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+    <t>Entity. Role, or Act</t>
   </si>
   <si>
     <t>Parameters.parameter.part</t>
@@ -1046,7 +1066,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="48.5546875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -2340,24 +2360,24 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2383,13 +2403,13 @@
         <v>143</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2415,13 +2435,13 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>75</v>
@@ -2439,7 +2459,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2448,24 +2468,24 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2491,13 +2511,13 @@
         <v>125</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2547,7 +2567,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2570,10 +2590,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2596,16 +2616,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2631,13 +2651,13 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>75</v>
@@ -2655,7 +2675,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2678,10 +2698,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2704,13 +2724,13 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2749,7 +2769,7 @@
         <v>75</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
@@ -2759,7 +2779,7 @@
         <v>137</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2768,24 +2788,24 @@
         <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2888,10 +2908,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2961,16 +2981,16 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>111</v>
@@ -2996,14 +3016,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3025,16 +3045,16 @@
         <v>104</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3083,7 +3103,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3101,15 +3121,15 @@
         <v>75</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3135,12 +3155,14 @@
         <v>98</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
@@ -3189,7 +3211,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>84</v>
@@ -3212,10 +3234,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3238,13 +3260,13 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3295,7 +3317,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3304,7 +3326,7 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>96</v>
@@ -3313,15 +3335,15 @@
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3344,16 +3366,16 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3403,7 +3425,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3412,7 +3434,7 @@
         <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>75</v>
@@ -3421,15 +3443,15 @@
         <v>75</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>75</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3455,13 +3477,13 @@
         <v>75</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3511,7 +3533,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3523,7 +3545,7 @@
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
@@ -3534,13 +3556,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -3562,13 +3584,13 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3619,7 +3641,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3628,24 +3650,24 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3748,10 +3770,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3821,16 +3843,16 @@
         <v>75</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>111</v>
@@ -3856,14 +3878,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -3885,16 +3907,16 @@
         <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -3943,7 +3965,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -3961,15 +3983,15 @@
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3995,12 +4017,14 @@
         <v>98</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4010,7 +4034,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -4049,7 +4073,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>84</v>
@@ -4072,10 +4096,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4098,13 +4122,13 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4155,7 +4179,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4164,7 +4188,7 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>96</v>
@@ -4173,15 +4197,15 @@
         <v>75</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4204,16 +4228,16 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4263,7 +4287,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4278,18 +4302,18 @@
         <v>75</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4315,13 +4339,13 @@
         <v>75</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4371,7 +4395,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4383,7 +4407,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-PAR-Close-Operation-Output.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-PAR-Close-Operation-Output.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="217">
   <si>
     <t>Property</t>
   </si>
@@ -486,16 +486,6 @@
     <t>Meta.security</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>Parameters.meta.tag</t>
   </si>
   <si>
@@ -622,9 +612,6 @@
     <t>The name of the parameter (reference to the operation definition).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Parameters.parameter.value[x]</t>
   </si>
   <si>
@@ -638,8 +625,8 @@
     <t>If the parameter is a data type.</t>
   </si>
   <si>
-    <t>ele-1
-inv-1</t>
+    <t xml:space="preserve">inv-1
+</t>
   </si>
   <si>
     <t>Parameters.parameter.resource</t>
@@ -656,13 +643,6 @@
   </si>
   <si>
     <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inv-1
-</t>
-  </si>
-  <si>
-    <t>Entity. Role, or Act</t>
   </si>
   <si>
     <t>Parameters.parameter.part</t>
@@ -1066,7 +1046,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="48.5546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -2360,24 +2340,24 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2403,13 +2383,13 @@
         <v>143</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2435,31 +2415,31 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2468,24 +2448,24 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2511,13 +2491,13 @@
         <v>125</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2567,7 +2547,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2590,10 +2570,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2616,16 +2596,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2651,31 +2631,31 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2698,10 +2678,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2724,13 +2704,13 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2769,7 +2749,7 @@
         <v>75</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
@@ -2779,7 +2759,7 @@
         <v>137</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2788,24 +2768,24 @@
         <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2908,10 +2888,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2981,16 +2961,16 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>111</v>
@@ -3016,14 +2996,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3045,16 +3025,16 @@
         <v>104</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3103,7 +3083,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3121,15 +3101,15 @@
         <v>75</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3155,14 +3135,12 @@
         <v>98</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
@@ -3211,7 +3189,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>84</v>
@@ -3234,10 +3212,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3260,13 +3238,13 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3317,7 +3295,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3326,7 +3304,7 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>96</v>
@@ -3335,15 +3313,15 @@
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3366,16 +3344,16 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3425,7 +3403,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3434,7 +3412,7 @@
         <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>75</v>
@@ -3443,15 +3421,15 @@
         <v>75</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3477,13 +3455,13 @@
         <v>75</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3533,7 +3511,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3545,7 +3523,7 @@
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
@@ -3556,13 +3534,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -3584,13 +3562,13 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3641,7 +3619,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3650,24 +3628,24 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3770,10 +3748,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3843,16 +3821,16 @@
         <v>75</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>111</v>
@@ -3878,14 +3856,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -3907,16 +3885,16 @@
         <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -3965,7 +3943,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -3983,15 +3961,15 @@
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4017,14 +3995,12 @@
         <v>98</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4034,7 +4010,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -4073,7 +4049,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>84</v>
@@ -4096,10 +4072,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4122,13 +4098,13 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4179,7 +4155,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4188,7 +4164,7 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>96</v>
@@ -4197,15 +4173,15 @@
         <v>75</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4228,16 +4204,16 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4287,7 +4263,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4302,18 +4278,18 @@
         <v>75</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4339,13 +4315,13 @@
         <v>75</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4395,7 +4371,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4407,7 +4383,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
